--- a/pseudodata/1110.xlsx
+++ b/pseudodata/1110.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,28 +536,28 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01206909718772261</v>
+        <v>0.001816671765467053</v>
       </c>
       <c r="M2" t="n">
-        <v>8.388270095008362e-05</v>
+        <v>0.0003234795269814023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006034548593861306</v>
+        <v>9.083358827335264e-05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -590,28 +590,28 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01339437826091238</v>
+        <v>0.001515316008085403</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001130724330524589</v>
+        <v>0.0003294402681306159</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006697189130456191</v>
+        <v>7.576580040427017e-05</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -644,28 +644,28 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01333253868967694</v>
+        <v>0.001076637533965002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001593900577473239</v>
+        <v>0.0003603890239344751</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0006666269344838471</v>
+        <v>5.38318766982501e-05</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -698,28 +698,28 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01218386455354501</v>
+        <v>0.0005387278976794317</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002272026906805538</v>
+        <v>0.0004193756316958189</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0006091932276772505</v>
+        <v>2.693639488397159e-05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -752,28 +752,28 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0103782370586076</v>
+        <v>-8.511408608476192e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000323651967496456</v>
+        <v>0.0005133820589206552</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005189118529303799</v>
+        <v>-4.255704304238096e-06</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -806,28 +806,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007888269438908102</v>
+        <v>-0.0007915284287954843</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004488284290384258</v>
+        <v>0.0006528999296491682</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003944134719454052</v>
+        <v>-3.957642143977421e-05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -860,28 +860,28 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004532652194154486</v>
+        <v>-0.001576963034672648</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005918166094427491</v>
+        <v>0.0008516869959018541</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002266326097077243</v>
+        <v>-7.88481517336324e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -908,34 +908,34 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000732912172919014</v>
+        <v>-0.002432181521915321</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001186280533320948</v>
+        <v>0.001126921161797146</v>
       </c>
       <c r="N9" t="n">
-        <v>3.66456086459507e-05</v>
+        <v>-0.000121609076095766</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -962,34 +962,34 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009028821527122683</v>
+        <v>-0.003338209024956007</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001599085683533111</v>
+        <v>0.001499706559066188</v>
       </c>
       <c r="N10" t="n">
-        <v>4.514410763561342e-05</v>
+        <v>-0.0001669104512478003</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1016,34 +1016,34 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0008517570351968822</v>
+        <v>-0.004258739360061448</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002254115813736962</v>
+        <v>0.001993243013997735</v>
       </c>
       <c r="N11" t="n">
-        <v>4.258785175984411e-05</v>
+        <v>-0.0002129369680030724</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1070,34 +1070,34 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000675204108927668</v>
+        <v>-0.005130849836868265</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0003213131265680984</v>
+        <v>0.002622967906073476</v>
       </c>
       <c r="N12" t="n">
-        <v>3.37602054463834e-05</v>
+        <v>-0.0002565424918434132</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1124,34 +1124,34 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004236826151968522</v>
+        <v>-0.005872186965562814</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0004577130019222242</v>
+        <v>0.003379425394263444</v>
       </c>
       <c r="N13" t="n">
-        <v>2.118413075984261e-05</v>
+        <v>-0.0002936093482781407</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1178,34 +1178,34 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001314971968988704</v>
+        <v>-0.006426443536978035</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0006347392515247521</v>
+        <v>0.004229115477048032</v>
       </c>
       <c r="N14" t="n">
-        <v>6.574859844943523e-06</v>
+        <v>-0.0003213221768489018</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1232,34 +1232,34 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0001246453898194211</v>
+        <v>-0.006812502555695149</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0008369550755115968</v>
+        <v>0.005161379235330389</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.232269490971055e-06</v>
+        <v>-0.0003406251277847575</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1286,34 +1286,34 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.000104461378325654</v>
+        <v>-0.007096156213429725</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001186280533320948</v>
+        <v>0.006234376010282524</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.223068916282702e-06</v>
+        <v>-0.0003548078106714863</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1340,34 +1340,34 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>6.423878474667353e-05</v>
+        <v>-0.007316705311159306</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001599085683533111</v>
+        <v>0.007542367229251986</v>
       </c>
       <c r="N17" t="n">
-        <v>3.211939237333677e-06</v>
+        <v>-0.0003658352655579653</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1394,631 +1394,37 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0001876325197905747</v>
+        <v>-0.007459172529753877</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0002254115813736962</v>
+        <v>0.009110715264989022</v>
       </c>
       <c r="N18" t="n">
-        <v>9.381625989528736e-06</v>
+        <v>-0.0003729586264876939</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.000248773330653805</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0003213131265680984</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.243866653269025e-05</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.000257060359501941</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0004577130019222242</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.285301797509705e-05</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0002206183857275422</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0006347392515247521</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.103091928637711e-05</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.0001679523754007734</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0008369550755115968</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.397618770038669e-06</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.236351105245078e-06</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.0001186280533320948</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6.181755526225391e-08</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>100</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>100</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-1.488908685336508e-05</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.0001599085683533111</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-7.444543426682542e-07</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-5.993812320315659e-06</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.0002254115813736962</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-2.996906160157829e-07</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>100</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.303799651020565e-05</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.0003213131265680984</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.151899825510283e-06</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>50</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.327029464978539e-05</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.0004577130019222242</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.163514732489269e-06</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.0001025105002842511</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.0006347392515247521</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.125525014212558e-06</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.0001390937322778411</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.0008369550755115968</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6.954686613892053e-06</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
         <v>1</v>
       </c>
     </row>
